--- a/config/role_figure.xlsx
+++ b/config/role_figure.xlsx
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>調査員</t>
+          <t>调查员</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>研究所の実験成果を調査するために雇われた物理学の研究家であり、研究所の爆発後に守護者となった</t>
+          <t>为了调查研究所的实验成果而被雇用的物理学研究家，在研究所爆炸后成为守护者。</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>レベル10に到達で解放</t>
+          <t>达到10级即可释放</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>調査員</t>
+          <t>调查员</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>研究所の実験成果を調査するために雇われた物理学の研究家であり、研究所の爆発後に守護者となった</t>
+          <t>为了调查研究所的实验成果而被雇用的物理学研究家，在研究所爆炸后成为守护者。</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>レベル10に到達で解放</t>
+          <t>达到10级即可释放</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>ナギサ</t>
+          <t>渚</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>海洋研究所の一員である彼女は、研究者だけでなく看護師でもある。感染後の彼女は、手中の針を武器として使用することもある。</t>
+          <t>作为海洋研究所的一员，她不仅是研究人员，也是护士。感染后的她，也会使用手中的针作为武器。</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>レベル45に到達で解放</t>
+          <t>达到45级后释放</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>アリーナ商店で購入可能</t>
+          <t>可在arena商店购买</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>レイ</t>
+          <t>雷</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>シレネ市の出身ではなく、神秘的な東洋からやってきた彼女は、全身から不思議な美しさを放っていた。 爆発の日、彼女はダンススタジオで、これから披露するダンスの練習をしていた。 その後、彼女はめったに踊らなくなったが、恐らくダンスを学んでいたことが関係して戦闘技術は格段に向上していた。</t>
+          <t>她并非锡勒内市出身，而是来自神秘的东方，全身散发出不可思议的美。爆炸那天，她正在舞蹈工作室练习即将表演的舞蹈。在那之后，她就很少跳舞了，不过大概是学跳舞的关系，战斗技术有了显著的提高。</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>レベル30に到達で解放</t>
+          <t>达到30级后释放</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>メイ</t>
+          <t>咪咪</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>元は教会の外部護衛だったが、超能力を得て創設者に認められ、今では神の力を信じるように。</t>
+          <t>原本是教会的外部护卫，但获得超能力后被创立者认可，现在相信神的力量。</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>我爱你</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>神職者として育ち、神への敬愛を胸に教会へ。超能力で杖を操り、今や無限の力を手にした。</t>
+          <t>作为神职人员长大，怀着对神的敬爱进入教会。用超能力操纵魔杖，现在获得了无限的力量。</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>レベル65に到達で解放</t>
+          <t>达到65级后释放</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>ナギサ</t>
+          <t>渚</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>海洋研究所の一員である彼女は、研究者だけでなく看護師でもある。感染後の彼女は、手中の針を武器として使用することもある。</t>
+          <t>作为海洋研究所的一员，她不仅是研究人员，也是护士。感染后的她，也会使用手中的针作为武器。</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>リチ</t>
+          <t>莉琪</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>山で育ち、父の死後に超能力を得た彼女。復讐を胸に、弓矢で真実を追い続ける。</t>
+          <t>在山上长大，父亲死后获得超能力的她。心怀复仇，用弓箭不断追求真相。</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>ギルド商店で購入可能</t>
+          <t>可在公会商店购买</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>リゼル</t>
+          <t>里塞尔</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>髪を切っている最中に爆発が起き、短髪に。超能力を得て、海島研究所でセキュリティを担当。</t>
+          <t>剪头发的时候发生爆炸，变成短发。获得超能力，在海岛研究所担任保安。</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>ノエル</t>
+          <t>诺埃尔</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>研究所の特殊部隊に所属していた彼女は、超能力者となった後、エネルギー砲を操る能力を身につけた。その結果、研究所に重宝され、研究所の新兵器の多くを使えるようになった。</t>
+          <t>隶属于研究所特殊部队的她，在成为超能力者后，获得了操纵能量炮的能力。结果被研究所视为珍宝，能够使用研究所的许多新武器。</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>エリート大会内交換獲得</t>
+          <t>精英大会内交换获得</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>サリー</t>
+          <t>莎莉</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>超能力者になった後、彼女の体力は急激に増加し、流星のような高度な武器すらも自在に使えるようになった。噂によれば、千代が彼女を弱々しいと嘲笑ったことで、彼女が無尽蔵の力を手に入れる原因となったと言われている。</t>
+          <t>成为超能力者后，她的体力急剧增加，甚至可以自由使用流星这样的高级武器。根据传闻，千代嘲笑她软弱，成为她获得无尽力量的原因。</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>イグナ</t>
+          <t>伊格纳</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>海島研究所のみんなが大好き。雷の力を操り、特製の絶縁手袋をプレゼントされた。</t>
+          <t>海岛研究所的大家都很喜欢。操纵雷的力量，被送了特制的绝缘手套。</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>チヨ</t>
+          <t>友谊</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>煙を操る力を持つ超能力者。アリサとは幼なじみで、共にギルドを支える頼れる存在。</t>
+          <t>拥有操纵烟雾能力的超能力者。与亚莉莎青梅竹马，是一起支撑公会的可靠存在。</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>リアルタイム対戦で交換可能</t>
+          <t>可在实时对战中交换</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>フラン</t>
+          <t>法郎</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>神の加護を受けたとされる少女。自然の力を悟り、同じ信仰を持つ者たちのもとで暮らしている。</t>
+          <t>受到神加护的少女。领悟自然的力量，与拥有相同信仰的人们一起生活。</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>リアルタイム対戦で交換可能</t>
+          <t>可在实时对战中交换</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>カレル</t>
+          <t>查理</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>彼はボクシングが得意で学生の頃からボクシングを習っていた。超能力者になってからは石を操る能力も身につけた。</t>
+          <t>他擅长拳击，从学生时代开始学习拳击。成为超能力者后也拥有了操纵石头的能力。</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>夢咲 千雪</t>
+          <t>梦咲千雪</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>彼女にギルドにいる理由を聞けば、間違いなく「ギルドの雰囲気が好きだから」と言うだろう。「災難に見舞われたとき、ヴィンセントが騎士のように助けてくれたから」とは絶対に言わない。その結果、二人とも怪我を負いながらも超能力者になったのだ。それがいいことなのかどうかはわからない。</t>
+          <t>如果问她留在公会的理由，她一定会回答“因为喜欢公会的氛围”。我绝对不会说“因为当我遇到灾难时，文森特像骑士一样帮助了我”。结果，两人都负伤成为超能力者。我不知道这是不是好事。</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>アドベンチャーライセンスのレベルがレベル5に達するとロック解除可能</t>
+          <t>冒险许可证等级达到5级后即可解锁</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>メグ</t>
+          <t>梅格</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>シラヌス闘技場で、肩の蛇と共にダンスを披露し観客を魅了。</t>
+          <t>在西拉努斯竞技场与肩蛇一起跳舞，吸引了众多观众。</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>マコ</t>
+          <t>mako</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>教会の表の顔である彼女。創設者から異能者としての能力を買われ、大きな権限を委ねられた。</t>
+          <t>她是教会的正面人物。被创立者看中作为异能者的能力，被委以很大的权限。</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>ギルド戦で購入可能</t>
+          <t>可以在公会战中购买</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>マホ</t>
+          <t>真帆</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>彼女のお楽しみは、闘技場にいるときに手にしたスレッジハンマーで対戦相手を打ちのめすことだった。しかし、爆発の際、彼女は足元がおぼつかず、そのフィールドに大きな穴を開けてしまい、審判のナナミにルール違反だと指摘された。 しかしその後、幸いなことに、彼女は超能力者となり、スレッジハンマーをパワフルに扱えるようになった。</t>
+          <t>她的乐趣就是在竞技场上用手中的雪橇锤击倒对手。但是，在爆炸的时候，她的脚步不稳，在场上踢出了一个大洞，被裁判奈奈美指出违反了规则。但幸运的是，她后来成为超能力者，能够有力地使用雪橇锤。</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>樱花</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>彼女は両親にとって従順でいい子な娘でだったが、超能力者になってからは携帯電話を使って攻撃できるようになった。安定しないこともあるが、一般人に変装することは非常に熟練している。</t>
+          <t>她对父母来说是个听话的乖女儿，但自从成为超能力者后就能使用手机攻击。虽然有时不稳定，但乔装成一般人非常熟练。</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ソールズ</t>
+          <t>索尔斯</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>风筝</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>元レストランの料理長。超能力で調理器具が進化し、今は船で料理しながら旅を満喫。</t>
+          <t>原餐厅的厨师长。由于超能力烹调器具进化，现在在船上一边料理一边享受旅行。</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>レベル75に到達で解放</t>
+          <t>达到75级后释放</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>カリナ</t>
+          <t>卡利纳</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>薪割り少女が超能力で斧の達人に。今はセランス闘技場で活躍中。</t>
+          <t>劈柴少女用超能力成为斧头高手。现在活跃于赛兰斯竞技场。</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>レベル20に到達で解放</t>
+          <t>达到20级即可释放</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>アリサ</t>
+          <t>艾丽莎</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>ギルド創設者として有名な彼女たが謎が多い。爆発で得た能力で、故郷を守り続けている。</t>
+          <t>作为公会创立者而出名的她有很多谜团。用爆炸获得的能力，持续守护着故乡。</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>時空激戦で購入可能</t>
+          <t>可以在时空激战中购买</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>リア</t>
+          <t>现</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>彼女は研究所のメンバーではなかったが、爆発後、特別な能力でピストルを自在に操って攻撃をすることができるようになった。努力の結果、体力も大幅に向上し、研究所から防衛チームのメンバーとして召集された。</t>
+          <t>她虽然不是研究所的成员，但在爆炸后，拥有了特别的能力，能够自由操纵手枪进行攻击。经过努力，体力也大幅提升，被研究所征召为防卫队的成员。</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>レベル55に到達で解放</t>
+          <t>达到55级后释放</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>リア</t>
+          <t>现</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>彼女は研究所のメンバーではなかったが、爆発後、特別な能力でピストルを自在に操って攻撃をすることができるようになった。努力の結果、体力も大幅に向上し、研究所から防衛チームのメンバーとして召集された。</t>
+          <t>她虽然不是研究所的成员，但在爆炸后，拥有了特别的能力，能够自由操纵手枪进行攻击。经过努力，体力也大幅提升，被研究所征召为防卫队的成员。</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>レベル10に到達で解放</t>
+          <t>达到10级即可释放</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>リア</t>
+          <t>现</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>彼女は航海船の所有者で、剣術と火の力で船と船員を守る超能力者になった。</t>
+          <t>她是航海船的所有者，成为了用剑术和火的力量保护船和船员的超能力者。</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>アリーナ商店で購入可能</t>
+          <t>可在arena商店购买</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>エリサ</t>
+          <t>艾丽莎</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>彼女は教会の使者で、神の導きを務めていた。しかし、災厄が訪れ、空に広がる巨大な亀裂が開いたとき、彼女もも感染し、異能者となった。その後、彼女の心には未来への不安が強くなり、神が彼らを救えるのか、という疑念を持った。</t>
+          <t>她是教会的使者，负责引导神。但是当灾难降临，天空中的巨大龟裂裂开时，她也被感染，成为了异能者。在那之后，她心中对未来的不安越来越强烈，甚至怀疑神是否能够拯救他们。</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ナンナン</t>
+          <t>南南</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>彼女の一家はカボチャの農場を経営しており、爆発の時もカボチャを植えていた。爆発の後、カボチャも影響を受け、変異したのだった。外観は少し怖いが、特別な乗り物が手に入ったため、彼女はとても喜んだ。彼女が選んだ服とカボチャを合わせると、まとまったファッションになるのであった。</t>
+          <t>她一家经营南瓜农场，爆炸发生时也在种南瓜。爆炸之后，南瓜也受到了影响，发生了变异。外观有点吓人，但她很高兴，因为她得到了一个特殊的车辆。她挑选的衣服和南瓜搭配在一起，就成了一种时尚。</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>ナナミ</t>
+          <t>七浪</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>シラヌスの闘技場のレフリーとして、すべての試合を公平に裁く責任があった。しかし、爆発の影響で10年間続けてきたレフリーの記録が途切れてしまったのである。その後も、闘技場への参加者はかなり熱心だったが、爆発がもたらした悔しさから練習に明け暮れる日々を送っていた。</t>
+          <t>作为西拉努斯竞技场的裁判，他有责任公平裁决所有比赛。但是，由于爆炸的影响，持续了10年的裁判记录中断了。在那之后，虽然参加竞技场的人都相当热心，但因为爆炸带来的悔恨，每天都过着练习的日子。</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>レイナ</t>
+          <t>雷纳</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>写真が好きな彼女は、超能力でカメラが武器に変わったが、写真の中の男性に心を動かされた。</t>
+          <t>喜欢摄影的她虽然因为超能力把相机变成了武器，但还是被照片中的男子所打动。</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>マリー</t>
+          <t>玛丽</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>爆発の影響を受け、彼女の槍は炎の魔力を発生させた。そのせいで、彼女は都市で注目を集めるようになった。</t>
+          <t>受到爆炸的影响，她的枪产生了火焰的魔力。因此，她开始受到城市的关注。</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>彼女はもともと都市のサーカス団でアクロバットをしていたが、感染して超能者となり、太刀を操る能力を手に入れた。その後、彼女は偶然にも森にたどり着き、ギルドに参加しました。孤独な彼女はここで多くの友達と出会った。ここで初めて、友情の意味を知ったのであった。</t>
+          <t>她原本在城市马戏团表演杂技，但受到感染而成为超能者，获得了操纵太刀的能力。后来，她偶然来到森林并加入了公会。孤独的她在这里认识了很多好友。在这里，我第一次明白了友情的意义。</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>航海をしていると、理由もなく襲ってくる輩がいるが、彼女がいる限り、問題ない。彼女は警備のプロフェッショナルであり、超能力者になってからは二刀流のコントロールにも長けている。別の街には、彼女と張り合おうとする二刀流の使い手がいるらしい。</t>
+          <t>航海的时候，有些人会无缘无故地袭击我，但只要她在，就不会有问题。她是警备方面的专家，成为超能力者后也擅长控制二刀流。在别的城市，似乎有想要和她竞争的二刀流高手。</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>アンナ</t>
+          <t>安娜</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>彼女の好きなイベントはクリスマスだった。航海の日々はとても退屈だが、イベントのときだけ皆が集まるため彼女はそこで暖かさを感じる。 超能力者になった後、母親から託されたホラ貝は武器となり、その力を使って船の仲間を守りたいと考えている。</t>
+          <t>她最喜欢的活动是圣诞节。航海的日子很无聊，但只有活动时大家才会聚集在一起，她在那里感到温暖。成为超能力者后，将母亲托付给他的海螺当作武器，想要用这个力量来保护船上的伙伴。</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>一条 ももこ</t>
+          <t>一条桃子</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>お金持ちになるのが夢だったが、超能力になってからは、皮肉なことに、金貨を使った攻撃が得意となった。</t>
+          <t>梦想是成为有钱人，但讽刺的是，在拥有超能力之后，变得擅长使用金币攻击。</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>シエル</t>
+          <t>夏尔</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>パソコンが得意で爆発後、プログラムをレーザー攻撃に変える能力を得たがコードがまだ未完成。</t>
+          <t>擅长电脑，爆炸后获得了将程序转换为激光攻击的能力，但代码尚未完成。</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>リアン</t>
+          <t>里昂</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>もともとは街の中心部に住んでいた少女だったが、超能力者として感染してからは手が鋭い鉤爪に変わり、感受性と運動能力が非常に高まったため、現在は森のギルドに住んでいる。</t>
+          <t>原本是住在城市中心的少女，但感染超能力者后手变成锐利的钩爪，感受性和运动能力非常高，现在住在森林的基尔特。</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ミミル</t>
+          <t>米米尔</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>限定イベントで獲得可能</t>
+          <t>可在限定活动中获得</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>イシス</t>
+          <t>伊西斯</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>レベル10に到達で解放</t>
+          <t>达到10级即可释放</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>シオリ</t>
+          <t>书签</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>ルナ</t>
+          <t>露娜</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>朝宮 香澄</t>
+          <t>朝宫香澄</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>イーグレ</t>
+          <t>伊格里</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>シャノン</t>
+          <t>香农</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>ナコ</t>
+          <t>奈子</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -14494,7 +14494,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>タクヤ</t>
+          <t>拓也</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>ハルト</t>
+          <t>哈尔特</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ヴィン</t>
+          <t>文恩</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
